--- a/data/Chemical_analysis_raw/251126_EEWORM_these_Lisa_soil_MIX.xlsx
+++ b/data/Chemical_analysis_raw/251126_EEWORM_these_Lisa_soil_MIX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdelarue\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\89UIZDII\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/Chemical_analysis_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD78B53-0BC7-43A8-8C2B-D79CB48E1188}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C34314E-F203-4547-9AA4-DA6BBC152294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7870" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="17220" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dose_epx_gamme basse" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,19 @@
     <sheet name="résultats" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -993,7 +1006,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1010,11 +1023,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1056,22 +1064,12 @@
     <xf numFmtId="165" fontId="14" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1139,6 +1137,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1495,45 +1494,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.08984375" customWidth="1"/>
-    <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" customWidth="1"/>
-    <col min="5" max="5" width="8.26953125" customWidth="1"/>
-    <col min="6" max="6" width="5.54296875" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" customWidth="1"/>
+    <col min="6" max="6" width="5.5" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" style="3"/>
-    <col min="10" max="10" width="4.6328125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.90625" style="3"/>
-    <col min="12" max="12" width="4.7265625" style="3" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="3"/>
-    <col min="16" max="16" width="3.26953125" customWidth="1"/>
-    <col min="17" max="17" width="10.90625" style="1"/>
-    <col min="18" max="18" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.90625" style="22"/>
-    <col min="21" max="21" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" style="3"/>
+    <col min="10" max="10" width="4.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="3"/>
+    <col min="12" max="12" width="4.6640625" style="3" customWidth="1"/>
+    <col min="13" max="14" width="10.83203125" style="3"/>
+    <col min="16" max="16" width="3.33203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" style="1"/>
+    <col min="18" max="18" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.83203125" style="19"/>
+    <col min="21" max="21" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>1</v>
       </c>
@@ -1577,7 +1576,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1618,7 +1617,7 @@
         <v>3.0760000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1659,7 +1658,7 @@
         <v>3.0179999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1700,7 +1699,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>3.0920000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1782,7 +1781,7 @@
         <v>3.2410000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>6</v>
       </c>
@@ -1823,7 +1822,7 @@
         <v>3.0459999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>7</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>2.911</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>8</v>
       </c>
@@ -1905,7 +1904,7 @@
         <v>2.9350000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>9</v>
       </c>
@@ -1946,7 +1945,7 @@
         <v>2.8380000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10</v>
       </c>
@@ -1987,7 +1986,7 @@
         <v>2.9569999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>49</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>50</v>
       </c>
@@ -2069,7 +2068,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>51</v>
       </c>
@@ -2110,7 +2109,7 @@
         <v>3.0190000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>52</v>
       </c>
@@ -2151,7 +2150,7 @@
         <v>2.9790000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>56</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>3.1379999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>11</v>
       </c>
@@ -2224,7 +2223,7 @@
         <v>2.8460000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>12</v>
       </c>
@@ -2256,7 +2255,7 @@
         <v>2.8969999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>13</v>
       </c>
@@ -2288,7 +2287,7 @@
         <v>3.1440000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>14</v>
       </c>
@@ -2320,7 +2319,7 @@
         <v>4.407</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>15</v>
       </c>
@@ -2349,7 +2348,7 @@
         <v>3.1709999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>16</v>
       </c>
@@ -2383,10 +2382,10 @@
       <c r="R28" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="S28" s="13" t="s">
+      <c r="S28" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="T28" s="23" t="s">
+      <c r="T28" s="20" t="s">
         <v>122</v>
       </c>
       <c r="U28" t="s">
@@ -2396,7 +2395,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>17</v>
       </c>
@@ -2425,7 +2424,7 @@
         <v>3.5630000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>18</v>
       </c>
@@ -2454,7 +2453,7 @@
         <v>3.5640000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>19</v>
       </c>
@@ -2491,16 +2490,16 @@
       <c r="R31" s="1">
         <v>5.0263</v>
       </c>
-      <c r="S31" s="25">
+      <c r="S31" s="22">
         <f>(H31*Q31*1.2/1000)*(7/0.4)</f>
         <v>1.0499999999999999E-3</v>
       </c>
-      <c r="T31" s="22">
+      <c r="T31" s="19">
         <f>S31*1000/R31</f>
         <v>0.20890117979428208</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>20</v>
       </c>
@@ -2537,16 +2536,16 @@
       <c r="R32" s="1">
         <v>4.96</v>
       </c>
-      <c r="S32" s="25">
+      <c r="S32" s="22">
         <f t="shared" ref="S32" si="0">(H32*Q32*1.2/1000)*(7/0.4)</f>
         <v>8.4000000000000003E-4</v>
       </c>
-      <c r="T32" s="22">
+      <c r="T32" s="19">
         <f t="shared" ref="T32:T52" si="1">S32*1000/R32</f>
         <v>0.16935483870967744</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>21</v>
       </c>
@@ -2580,9 +2579,9 @@
       <c r="R33" s="1">
         <v>4.95</v>
       </c>
-      <c r="S33" s="25"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="S33" s="22"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>22</v>
       </c>
@@ -2619,16 +2618,16 @@
       <c r="R34" s="1">
         <v>4.9660000000000002</v>
       </c>
-      <c r="S34" s="25">
+      <c r="S34" s="22">
         <f t="shared" ref="S34:S52" si="2">(H34*Q34*1.2/1000)*(7/0.1)</f>
         <v>1.6799999999999999E-2</v>
       </c>
-      <c r="T34" s="22">
+      <c r="T34" s="19">
         <f t="shared" si="1"/>
         <v>3.3830044301248492</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>23</v>
       </c>
@@ -2662,9 +2661,9 @@
       <c r="R35" s="1">
         <v>4.9333999999999998</v>
       </c>
-      <c r="S35" s="25"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="S35" s="22"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>24</v>
       </c>
@@ -2698,66 +2697,66 @@
       <c r="R36" s="1">
         <v>4.9353999999999996</v>
       </c>
-      <c r="S36" s="25"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A37" s="16">
+      <c r="S36" s="22"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A37" s="13">
         <v>25</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17">
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="14">
         <v>5.73</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="15">
         <v>154756</v>
       </c>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18">
+      <c r="J37" s="15"/>
+      <c r="K37" s="15">
         <v>154756.391</v>
       </c>
-      <c r="L37" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M37" s="18">
+      <c r="L37" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" s="15">
         <v>52014.07</v>
       </c>
-      <c r="N37" s="18">
+      <c r="N37" s="15">
         <v>2885.3679999999999</v>
       </c>
-      <c r="O37" s="16">
+      <c r="O37" s="13">
         <v>2.9750000000000001</v>
       </c>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="19">
+      <c r="P37" s="13"/>
+      <c r="Q37" s="16">
         <v>60</v>
       </c>
-      <c r="R37" s="20">
+      <c r="R37" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S37" s="21">
+      <c r="S37" s="18">
         <f t="shared" si="2"/>
         <v>28.879199999999997</v>
       </c>
-      <c r="T37" s="33">
+      <c r="T37" s="27">
         <f t="shared" si="1"/>
         <v>5740.2504472271912</v>
       </c>
-      <c r="U37" s="21">
+      <c r="U37" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V37" s="24">
+      <c r="V37" s="21">
         <f>(S37-S31)*100/U37</f>
         <v>101.46034255599471</v>
       </c>
@@ -2765,69 +2764,69 @@
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A38" s="16">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A38" s="13">
         <v>26</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G38" s="16"/>
-      <c r="H38" s="17">
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14">
         <v>5.68</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="15">
         <v>153430</v>
       </c>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18">
+      <c r="J38" s="15"/>
+      <c r="K38" s="15">
         <v>153430.109</v>
       </c>
-      <c r="L38" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M38" s="18">
+      <c r="L38" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M38" s="15">
         <v>51536.620999999999</v>
       </c>
-      <c r="N38" s="18">
+      <c r="N38" s="15">
         <v>3702.8530000000001</v>
       </c>
-      <c r="O38" s="16">
+      <c r="O38" s="13">
         <v>2.9769999999999999</v>
       </c>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="19">
+      <c r="P38" s="13"/>
+      <c r="Q38" s="16">
         <v>60</v>
       </c>
-      <c r="R38" s="20">
+      <c r="R38" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S38" s="21">
+      <c r="S38" s="18">
         <f t="shared" si="2"/>
         <v>28.627199999999995</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="27">
         <f t="shared" si="1"/>
         <v>5690.1610017889079</v>
       </c>
-      <c r="U38" s="21">
+      <c r="U38" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V38" s="24">
+      <c r="V38" s="21">
         <f>(S38-S32)*100/U38</f>
         <v>100.57570487483528</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>27</v>
       </c>
@@ -2864,16 +2863,16 @@
       <c r="R39" s="1">
         <v>4.9870000000000001</v>
       </c>
-      <c r="S39" s="14">
+      <c r="S39" s="11">
         <f t="shared" si="2"/>
         <v>7.0728</v>
       </c>
-      <c r="T39" s="34">
+      <c r="T39" s="28">
         <f t="shared" si="1"/>
         <v>1418.247443352717</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>28</v>
       </c>
@@ -2910,16 +2909,16 @@
       <c r="R40" s="1">
         <v>4.9539999999999997</v>
       </c>
-      <c r="S40" s="14">
+      <c r="S40" s="11">
         <f t="shared" si="2"/>
         <v>10.768799999999999</v>
       </c>
-      <c r="T40" s="34">
+      <c r="T40" s="28">
         <f t="shared" si="1"/>
         <v>2173.7585789261202</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>29</v>
       </c>
@@ -2956,16 +2955,16 @@
       <c r="R41" s="1">
         <v>5.0216000000000003</v>
       </c>
-      <c r="S41" s="14">
+      <c r="S41" s="11">
         <f t="shared" si="2"/>
         <v>17.6736</v>
       </c>
-      <c r="T41" s="34">
+      <c r="T41" s="28">
         <f t="shared" si="1"/>
         <v>3519.5156922096544</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>30</v>
       </c>
@@ -3002,73 +3001,73 @@
       <c r="R42" s="1">
         <v>5.0906000000000002</v>
       </c>
-      <c r="S42" s="14">
+      <c r="S42" s="11">
         <f t="shared" si="2"/>
         <v>18.731999999999996</v>
       </c>
-      <c r="T42" s="34">
+      <c r="T42" s="28">
         <f t="shared" si="1"/>
         <v>3679.7234117785715</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A43" s="16">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A43" s="13">
         <v>31</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="17">
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="14">
         <v>17.87</v>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="15">
         <v>458944</v>
       </c>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18">
+      <c r="J43" s="15"/>
+      <c r="K43" s="15">
         <v>458943.90600000002</v>
       </c>
-      <c r="L43" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M43" s="18">
+      <c r="L43" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="15">
         <v>153531.95300000001</v>
       </c>
-      <c r="N43" s="18">
+      <c r="N43" s="15">
         <v>4813.8029999999999</v>
       </c>
-      <c r="O43" s="16">
+      <c r="O43" s="13">
         <v>2.9889999999999999</v>
       </c>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="19">
+      <c r="P43" s="13"/>
+      <c r="Q43" s="16">
         <v>20</v>
       </c>
-      <c r="R43" s="20">
+      <c r="R43" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S43" s="21">
+      <c r="S43" s="18">
         <f t="shared" si="2"/>
         <v>30.021600000000003</v>
       </c>
-      <c r="T43" s="33">
+      <c r="T43" s="27">
         <f t="shared" si="1"/>
         <v>5967.3225998807402</v>
       </c>
-      <c r="U43" s="21">
+      <c r="U43" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V43" s="24">
+      <c r="V43" s="21">
         <f>(S43-S31)*100/U43</f>
         <v>105.47404479578393</v>
       </c>
@@ -3076,69 +3075,69 @@
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A44" s="16">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A44" s="13">
         <v>32</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G44" s="16"/>
-      <c r="H44" s="17">
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="14">
         <v>17.52</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="15">
         <v>450574</v>
       </c>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18">
+      <c r="J44" s="15"/>
+      <c r="K44" s="15">
         <v>450573.78100000002</v>
       </c>
-      <c r="L44" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M44" s="18">
+      <c r="L44" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="15">
         <v>148063.04699999999</v>
       </c>
-      <c r="N44" s="18">
+      <c r="N44" s="15">
         <v>3452.9059999999999</v>
       </c>
-      <c r="O44" s="16">
+      <c r="O44" s="13">
         <v>3.0430000000000001</v>
       </c>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="19">
+      <c r="P44" s="13"/>
+      <c r="Q44" s="16">
         <v>20</v>
       </c>
-      <c r="R44" s="20">
+      <c r="R44" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S44" s="21">
+      <c r="S44" s="18">
         <f t="shared" si="2"/>
         <v>29.433599999999998</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="27">
         <f t="shared" si="1"/>
         <v>5850.4472271914137</v>
       </c>
-      <c r="U44" s="21">
+      <c r="U44" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V44" s="24">
+      <c r="V44" s="21">
         <f>(S43-S32)*100/U44</f>
         <v>105.47478260869566</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>33</v>
       </c>
@@ -3175,16 +3174,16 @@
       <c r="R45" s="1">
         <v>5.0460000000000003</v>
       </c>
-      <c r="S45" s="14">
+      <c r="S45" s="11">
         <f t="shared" si="2"/>
         <v>26.023199999999999</v>
       </c>
-      <c r="T45" s="34">
+      <c r="T45" s="28">
         <f t="shared" si="1"/>
         <v>5157.1938168846609</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>34</v>
       </c>
@@ -3221,16 +3220,16 @@
       <c r="R46" s="1">
         <v>5.0867000000000004</v>
       </c>
-      <c r="S46" s="14">
+      <c r="S46" s="11">
         <f t="shared" si="2"/>
         <v>26.359200000000001</v>
       </c>
-      <c r="T46" s="34">
+      <c r="T46" s="28">
         <f t="shared" si="1"/>
         <v>5181.9843906658534</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>35</v>
       </c>
@@ -3267,16 +3266,16 @@
       <c r="R47" s="1">
         <v>4.9630000000000001</v>
       </c>
-      <c r="S47" s="14">
+      <c r="S47" s="11">
         <f t="shared" si="2"/>
         <v>33.734399999999994</v>
       </c>
-      <c r="T47" s="34">
+      <c r="T47" s="28">
         <f t="shared" si="1"/>
         <v>6797.1791255289127</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>36</v>
       </c>
@@ -3313,16 +3312,16 @@
       <c r="R48" s="1">
         <v>5.0391000000000004</v>
       </c>
-      <c r="S48" s="14">
+      <c r="S48" s="11">
         <f t="shared" si="2"/>
         <v>35.380799999999994</v>
       </c>
-      <c r="T48" s="34">
+      <c r="T48" s="28">
         <f t="shared" si="1"/>
         <v>7021.253795320592</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>37</v>
       </c>
@@ -3359,22 +3358,22 @@
         <v>2.9489999999999998</v>
       </c>
       <c r="P49" s="4"/>
-      <c r="Q49" s="11">
+      <c r="Q49" s="8">
         <v>60</v>
       </c>
-      <c r="R49" s="12">
+      <c r="R49" s="9">
         <v>5.0975999999999999</v>
       </c>
-      <c r="S49" s="15">
+      <c r="S49" s="12">
         <f t="shared" si="2"/>
         <v>183.75839999999999</v>
       </c>
-      <c r="T49" s="36">
+      <c r="T49" s="29">
         <f t="shared" si="1"/>
         <v>36048.022598870055</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>38</v>
       </c>
@@ -3411,22 +3410,22 @@
         <v>3.048</v>
       </c>
       <c r="P50" s="4"/>
-      <c r="Q50" s="11">
+      <c r="Q50" s="8">
         <v>60</v>
       </c>
-      <c r="R50" s="12">
+      <c r="R50" s="9">
         <v>4.9290000000000003</v>
       </c>
-      <c r="S50" s="15">
+      <c r="S50" s="12">
         <f t="shared" si="2"/>
         <v>178.46639999999999</v>
       </c>
-      <c r="T50" s="36">
+      <c r="T50" s="29">
         <f t="shared" si="1"/>
         <v>36207.425441265972</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>39</v>
       </c>
@@ -3463,22 +3462,22 @@
         <v>3.0230000000000001</v>
       </c>
       <c r="P51" s="4"/>
-      <c r="Q51" s="11">
+      <c r="Q51" s="8">
         <v>60</v>
       </c>
-      <c r="R51" s="12">
+      <c r="R51" s="9">
         <v>4.992</v>
       </c>
-      <c r="S51" s="15">
+      <c r="S51" s="12">
         <f t="shared" si="2"/>
         <v>373.46399999999994</v>
       </c>
-      <c r="T51" s="36">
+      <c r="T51" s="29">
         <f t="shared" si="1"/>
         <v>74812.499999999985</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>40</v>
       </c>
@@ -3515,22 +3514,22 @@
         <v>3.1120000000000001</v>
       </c>
       <c r="P52" s="4"/>
-      <c r="Q52" s="11">
+      <c r="Q52" s="8">
         <v>60</v>
       </c>
-      <c r="R52" s="12">
+      <c r="R52" s="9">
         <v>5.0566000000000004</v>
       </c>
-      <c r="S52" s="15">
+      <c r="S52" s="12">
         <f t="shared" si="2"/>
         <v>411.3648</v>
       </c>
-      <c r="T52" s="36">
+      <c r="T52" s="29">
         <f t="shared" si="1"/>
         <v>81352.054740339343</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>41</v>
       </c>
@@ -3565,18 +3564,18 @@
         <v>3.0579999999999998</v>
       </c>
       <c r="P53" s="4"/>
-      <c r="Q53" s="11">
+      <c r="Q53" s="8">
         <v>60</v>
       </c>
-      <c r="R53" s="12">
+      <c r="R53" s="9">
         <v>4.9340000000000002</v>
       </c>
-      <c r="S53" s="27" t="s">
+      <c r="S53" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="T53" s="26"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T53" s="23"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>42</v>
       </c>
@@ -3611,18 +3610,18 @@
         <v>2.98</v>
       </c>
       <c r="P54" s="4"/>
-      <c r="Q54" s="11">
+      <c r="Q54" s="8">
         <v>60</v>
       </c>
-      <c r="R54" s="12">
+      <c r="R54" s="9">
         <v>5.0629999999999997</v>
       </c>
-      <c r="S54" s="27" t="s">
+      <c r="S54" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="T54" s="26"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T54" s="23"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>43</v>
       </c>
@@ -3657,18 +3656,18 @@
         <v>2.9449999999999998</v>
       </c>
       <c r="P55" s="4"/>
-      <c r="Q55" s="11">
+      <c r="Q55" s="8">
         <v>60</v>
       </c>
-      <c r="R55" s="12">
+      <c r="R55" s="9">
         <v>4.9804000000000004</v>
       </c>
-      <c r="S55" s="27" t="s">
+      <c r="S55" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="T55" s="26"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="T55" s="23"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>44</v>
       </c>
@@ -3703,271 +3702,234 @@
         <v>3.004</v>
       </c>
       <c r="P56" s="4"/>
-      <c r="Q56" s="11">
+      <c r="Q56" s="8">
         <v>60</v>
       </c>
-      <c r="R56" s="12">
+      <c r="R56" s="9">
         <v>50.62</v>
       </c>
-      <c r="S56" s="27" t="s">
+      <c r="S56" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="T56" s="26"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A57" s="8">
+      <c r="T56" s="23"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>45</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" t="s">
         <v>114</v>
       </c>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8">
-        <v>10.49</v>
-      </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="9">
+      <c r="F57">
+        <v>10.49</v>
+      </c>
+      <c r="H57" s="2">
         <v>0.13</v>
       </c>
-      <c r="I57" s="10">
+      <c r="I57" s="3">
         <v>4264</v>
       </c>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10">
+      <c r="K57" s="3">
         <v>4264.2539999999999</v>
       </c>
-      <c r="L57" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M57" s="10">
+      <c r="L57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M57" s="3">
         <v>1249.4079999999999</v>
       </c>
-      <c r="N57" s="10">
+      <c r="N57" s="3">
         <v>250.09</v>
       </c>
-      <c r="O57" s="8">
+      <c r="O57">
         <v>3.4129999999999998</v>
       </c>
       <c r="Q57" s="7"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A58" s="8">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A58">
         <v>46</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8">
-        <v>10.49</v>
-      </c>
-      <c r="G58" s="8"/>
-      <c r="H58" s="9">
+      <c r="F58">
+        <v>10.49</v>
+      </c>
+      <c r="H58" s="2">
         <v>0.03</v>
       </c>
-      <c r="I58" s="10">
+      <c r="I58" s="3">
         <v>1377</v>
       </c>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10">
+      <c r="K58" s="3">
         <v>1377.0509999999999</v>
       </c>
-      <c r="L58" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M58" s="10">
+      <c r="L58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M58" s="3">
         <v>452.31599999999997</v>
       </c>
-      <c r="N58" s="10">
+      <c r="N58" s="3">
         <v>132.61000000000001</v>
       </c>
-      <c r="O58" s="8">
+      <c r="O58">
         <v>3.044</v>
       </c>
       <c r="Q58" s="7"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A59" s="8">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A59">
         <v>47</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" t="s">
         <v>116</v>
       </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8">
-        <v>10.49</v>
-      </c>
-      <c r="G59" s="8"/>
-      <c r="H59" s="9">
+      <c r="F59">
+        <v>10.49</v>
+      </c>
+      <c r="H59" s="2">
         <v>0.01</v>
       </c>
-      <c r="I59" s="10">
+      <c r="I59" s="3">
         <v>804</v>
       </c>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10">
+      <c r="K59" s="3">
         <v>803.69299999999998</v>
       </c>
-      <c r="L59" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M59" s="10">
+      <c r="L59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M59" s="3">
         <v>262.49299999999999</v>
       </c>
-      <c r="N59" s="10">
+      <c r="N59" s="3">
         <v>67.453000000000003</v>
       </c>
-      <c r="O59" s="8">
+      <c r="O59">
         <v>3.0619999999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A60" s="8">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A60">
         <v>48</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8">
-        <v>10.49</v>
-      </c>
-      <c r="G60" s="8"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10">
+      <c r="F60">
+        <v>10.49</v>
+      </c>
+      <c r="I60" s="3">
         <v>317</v>
       </c>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10">
+      <c r="K60" s="3">
         <v>316.56400000000002</v>
       </c>
-      <c r="L60" s="10" t="s">
+      <c r="L60" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M60" s="10">
+      <c r="M60" s="3">
         <v>77.265000000000001</v>
       </c>
-      <c r="N60" s="10">
+      <c r="N60" s="3">
         <v>50.988</v>
       </c>
-      <c r="O60" s="8">
+      <c r="O60">
         <v>4.0970000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A61" s="8">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A61">
         <v>53</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" t="s">
         <v>33</v>
       </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8">
-        <v>10.49</v>
-      </c>
-      <c r="G61" s="8"/>
-      <c r="H61" s="9">
+      <c r="F61">
+        <v>10.49</v>
+      </c>
+      <c r="H61" s="2">
         <v>0.24</v>
       </c>
-      <c r="I61" s="10">
+      <c r="I61" s="3">
         <v>7258</v>
       </c>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10">
+      <c r="K61" s="3">
         <v>7257.9390000000003</v>
       </c>
-      <c r="L61" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M61" s="10">
+      <c r="L61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M61" s="3">
         <v>2405.7199999999998</v>
       </c>
-      <c r="N61" s="10">
+      <c r="N61" s="3">
         <v>582.18100000000004</v>
       </c>
-      <c r="O61" s="8">
+      <c r="O61">
         <v>3.0169999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A62" s="8">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A62">
         <v>54</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" t="s">
         <v>35</v>
       </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8">
-        <v>10.49</v>
-      </c>
-      <c r="G62" s="8"/>
-      <c r="H62" s="9">
+      <c r="F62">
+        <v>10.49</v>
+      </c>
+      <c r="H62" s="2">
         <v>0.03</v>
       </c>
-      <c r="I62" s="10">
+      <c r="I62" s="3">
         <v>1431</v>
       </c>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10">
+      <c r="K62" s="3">
         <v>1431.15</v>
       </c>
-      <c r="L62" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="M62" s="10">
+      <c r="L62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M62" s="3">
         <v>465.49200000000002</v>
       </c>
-      <c r="N62" s="10">
+      <c r="N62" s="3">
         <v>145.089</v>
       </c>
-      <c r="O62" s="8">
+      <c r="O62">
         <v>3.0750000000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A63" s="8">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A63">
         <v>55</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" t="s">
         <v>36</v>
       </c>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8">
-        <v>10.49</v>
-      </c>
-      <c r="G63" s="8"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10">
+      <c r="F63">
+        <v>10.49</v>
+      </c>
+      <c r="I63" s="3">
         <v>408</v>
       </c>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10">
+      <c r="K63" s="3">
         <v>407.54199999999997</v>
       </c>
-      <c r="L63" s="10" t="s">
+      <c r="L63" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M63" s="10">
+      <c r="M63" s="3">
         <v>147.45400000000001</v>
       </c>
-      <c r="N63" s="10">
+      <c r="N63" s="3">
         <v>36.661999999999999</v>
       </c>
-      <c r="O63" s="8">
+      <c r="O63">
         <v>2.7639999999999998</v>
       </c>
     </row>
@@ -3980,45 +3942,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.36328125" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" customWidth="1"/>
-    <col min="5" max="5" width="7.36328125" customWidth="1"/>
-    <col min="6" max="6" width="4.90625" customWidth="1"/>
-    <col min="7" max="7" width="5.54296875" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" style="2"/>
-    <col min="9" max="9" width="10.90625" style="3"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.5" customWidth="1"/>
+    <col min="5" max="5" width="7.33203125" customWidth="1"/>
+    <col min="6" max="6" width="4.83203125" customWidth="1"/>
+    <col min="7" max="7" width="5.5" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="2"/>
+    <col min="9" max="9" width="10.83203125" style="3"/>
     <col min="10" max="10" width="5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.90625" style="3"/>
-    <col min="12" max="12" width="6.08984375" style="3" customWidth="1"/>
-    <col min="13" max="14" width="10.90625" style="3"/>
-    <col min="16" max="16" width="2.7265625" customWidth="1"/>
-    <col min="17" max="17" width="10.90625" style="1"/>
-    <col min="18" max="18" width="15.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.90625" style="22"/>
-    <col min="21" max="21" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="3"/>
+    <col min="12" max="12" width="6.1640625" style="3" customWidth="1"/>
+    <col min="13" max="14" width="10.83203125" style="3"/>
+    <col min="16" max="16" width="2.6640625" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" style="1"/>
+    <col min="18" max="18" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.83203125" style="19"/>
+    <col min="21" max="21" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>1</v>
       </c>
@@ -4062,7 +4024,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -4103,7 +4065,7 @@
         <v>3.0760000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -4144,7 +4106,7 @@
         <v>3.0179999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -4187,7 +4149,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>4</v>
       </c>
@@ -4230,7 +4192,7 @@
         <v>3.0920000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>5</v>
       </c>
@@ -4273,7 +4235,7 @@
         <v>3.2410000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>6</v>
       </c>
@@ -4314,7 +4276,7 @@
         <v>3.0459999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>7</v>
       </c>
@@ -4355,7 +4317,7 @@
         <v>2.911</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>8</v>
       </c>
@@ -4396,7 +4358,7 @@
         <v>2.9350000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>9</v>
       </c>
@@ -4437,7 +4399,7 @@
         <v>2.8380000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>10</v>
       </c>
@@ -4478,7 +4440,7 @@
         <v>2.9569999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>49</v>
       </c>
@@ -4521,7 +4483,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>50</v>
       </c>
@@ -4562,7 +4524,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>51</v>
       </c>
@@ -4603,7 +4565,7 @@
         <v>3.0190000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>52</v>
       </c>
@@ -4644,7 +4606,7 @@
         <v>2.9790000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>56</v>
       </c>
@@ -4685,7 +4647,7 @@
         <v>3.1379999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>11</v>
       </c>
@@ -4714,7 +4676,7 @@
         <v>2.8460000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>12</v>
       </c>
@@ -4743,7 +4705,7 @@
         <v>2.8969999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>13</v>
       </c>
@@ -4772,7 +4734,7 @@
         <v>3.1440000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>14</v>
       </c>
@@ -4801,7 +4763,7 @@
         <v>4.407</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>15</v>
       </c>
@@ -4830,7 +4792,7 @@
         <v>3.1709999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>16</v>
       </c>
@@ -4864,10 +4826,10 @@
       <c r="R28" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="S28" s="13" t="s">
+      <c r="S28" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="T28" s="23" t="s">
+      <c r="T28" s="20" t="s">
         <v>122</v>
       </c>
       <c r="U28" t="s">
@@ -4877,7 +4839,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>17</v>
       </c>
@@ -4912,14 +4874,14 @@
         <v>3.5630000000000002</v>
       </c>
       <c r="P29" s="4"/>
-      <c r="Q29" s="12"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="26"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="23"/>
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>18</v>
       </c>
@@ -4954,14 +4916,14 @@
         <v>3.5640000000000001</v>
       </c>
       <c r="P30" s="4"/>
-      <c r="Q30" s="12"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="31"/>
-      <c r="T30" s="26"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="23"/>
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>19</v>
       </c>
@@ -4996,18 +4958,18 @@
         <v>3.0529999999999999</v>
       </c>
       <c r="P31" s="4"/>
-      <c r="Q31" s="11">
+      <c r="Q31" s="8">
         <v>1</v>
       </c>
-      <c r="R31" s="12">
+      <c r="R31" s="9">
         <v>5.0263</v>
       </c>
-      <c r="S31" s="32"/>
-      <c r="T31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="23"/>
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>20</v>
       </c>
@@ -5042,18 +5004,18 @@
         <v>2.5339999999999998</v>
       </c>
       <c r="P32" s="4"/>
-      <c r="Q32" s="11">
+      <c r="Q32" s="8">
         <v>1</v>
       </c>
-      <c r="R32" s="12">
+      <c r="R32" s="9">
         <v>4.96</v>
       </c>
-      <c r="S32" s="32"/>
-      <c r="T32" s="26"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="23"/>
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>21</v>
       </c>
@@ -5088,18 +5050,18 @@
         <v>2.762</v>
       </c>
       <c r="P33" s="4"/>
-      <c r="Q33" s="11">
+      <c r="Q33" s="8">
         <v>20</v>
       </c>
-      <c r="R33" s="12">
+      <c r="R33" s="9">
         <v>4.95</v>
       </c>
-      <c r="S33" s="32"/>
-      <c r="T33" s="26"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="23"/>
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>22</v>
       </c>
@@ -5134,18 +5096,18 @@
         <v>3.2730000000000001</v>
       </c>
       <c r="P34" s="4"/>
-      <c r="Q34" s="11">
+      <c r="Q34" s="8">
         <v>20</v>
       </c>
-      <c r="R34" s="12">
+      <c r="R34" s="9">
         <v>4.9660000000000002</v>
       </c>
-      <c r="S34" s="32"/>
-      <c r="T34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="23"/>
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>23</v>
       </c>
@@ -5180,18 +5142,18 @@
         <v>3.6179999999999999</v>
       </c>
       <c r="P35" s="4"/>
-      <c r="Q35" s="11">
+      <c r="Q35" s="8">
         <v>20</v>
       </c>
-      <c r="R35" s="12">
+      <c r="R35" s="9">
         <v>4.9333999999999998</v>
       </c>
-      <c r="S35" s="32"/>
-      <c r="T35" s="26"/>
+      <c r="S35" s="26"/>
+      <c r="T35" s="23"/>
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>24</v>
       </c>
@@ -5226,75 +5188,75 @@
         <v>3.3849999999999998</v>
       </c>
       <c r="P36" s="4"/>
-      <c r="Q36" s="11">
+      <c r="Q36" s="8">
         <v>20</v>
       </c>
-      <c r="R36" s="12">
+      <c r="R36" s="9">
         <v>4.9353999999999996</v>
       </c>
-      <c r="S36" s="32"/>
-      <c r="T36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="23"/>
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A37" s="16">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A37" s="13">
         <v>25</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17">
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G37" s="13"/>
+      <c r="H37" s="14">
         <v>5.99</v>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="15">
         <v>154756</v>
       </c>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18">
+      <c r="J37" s="15"/>
+      <c r="K37" s="15">
         <v>154756.391</v>
       </c>
-      <c r="L37" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M37" s="18">
+      <c r="L37" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" s="15">
         <v>52014.07</v>
       </c>
-      <c r="N37" s="18">
+      <c r="N37" s="15">
         <v>2885.3679999999999</v>
       </c>
-      <c r="O37" s="16">
+      <c r="O37" s="13">
         <v>2.9750000000000001</v>
       </c>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="19">
+      <c r="P37" s="13"/>
+      <c r="Q37" s="16">
         <v>60</v>
       </c>
-      <c r="R37" s="20">
+      <c r="R37" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S37" s="21">
+      <c r="S37" s="18">
         <f t="shared" ref="S37:S56" si="0">(H37*Q37*1.2/1000)*(7/0.1)</f>
         <v>30.189600000000002</v>
       </c>
-      <c r="T37" s="33">
+      <c r="T37" s="27">
         <f t="shared" ref="T37:T56" si="1">S37*1000/R37</f>
         <v>6000.7155635062618</v>
       </c>
-      <c r="U37" s="21">
+      <c r="U37" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V37" s="24">
+      <c r="V37" s="21">
         <f>(S37-S31)*100/U37</f>
         <v>106.06798418972332</v>
       </c>
@@ -5302,69 +5264,69 @@
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A38" s="16">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A38" s="13">
         <v>26</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G38" s="16"/>
-      <c r="H38" s="17">
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14">
         <v>5.93</v>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="15">
         <v>153430</v>
       </c>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18">
+      <c r="J38" s="15"/>
+      <c r="K38" s="15">
         <v>153430.109</v>
       </c>
-      <c r="L38" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M38" s="18">
+      <c r="L38" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M38" s="15">
         <v>51536.620999999999</v>
       </c>
-      <c r="N38" s="18">
+      <c r="N38" s="15">
         <v>3702.8530000000001</v>
       </c>
-      <c r="O38" s="16">
+      <c r="O38" s="13">
         <v>2.9769999999999999</v>
       </c>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="19">
+      <c r="P38" s="13"/>
+      <c r="Q38" s="16">
         <v>60</v>
       </c>
-      <c r="R38" s="20">
+      <c r="R38" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S38" s="21">
+      <c r="S38" s="18">
         <f t="shared" si="0"/>
         <v>29.887199999999993</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="27">
         <f t="shared" si="1"/>
         <v>5940.6082289803207</v>
       </c>
-      <c r="U38" s="21">
+      <c r="U38" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V38" s="24">
+      <c r="V38" s="21">
         <f>(S38-S32)*100/U38</f>
         <v>105.00553359683791</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>27</v>
       </c>
@@ -5401,16 +5363,16 @@
       <c r="R39" s="1">
         <v>4.9870000000000001</v>
       </c>
-      <c r="S39" s="14">
+      <c r="S39" s="11">
         <f t="shared" si="0"/>
         <v>7.2576000000000009</v>
       </c>
-      <c r="T39" s="34">
+      <c r="T39" s="28">
         <f t="shared" si="1"/>
         <v>1455.3037898536197</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>28</v>
       </c>
@@ -5447,16 +5409,16 @@
       <c r="R40" s="1">
         <v>4.9539999999999997</v>
       </c>
-      <c r="S40" s="14">
+      <c r="S40" s="11">
         <f t="shared" si="0"/>
         <v>11.2896</v>
       </c>
-      <c r="T40" s="34">
+      <c r="T40" s="28">
         <f t="shared" si="1"/>
         <v>2278.8857488897861</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>29</v>
       </c>
@@ -5493,16 +5455,16 @@
       <c r="R41" s="1">
         <v>5.0216000000000003</v>
       </c>
-      <c r="S41" s="14">
+      <c r="S41" s="11">
         <f t="shared" si="0"/>
         <v>18.6648</v>
       </c>
-      <c r="T41" s="34">
+      <c r="T41" s="28">
         <f t="shared" si="1"/>
         <v>3716.9029791301573</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>30</v>
       </c>
@@ -5539,73 +5501,73 @@
       <c r="R42" s="1">
         <v>5.0906000000000002</v>
       </c>
-      <c r="S42" s="14">
+      <c r="S42" s="11">
         <f t="shared" si="0"/>
         <v>19.773599999999998</v>
       </c>
-      <c r="T42" s="34">
+      <c r="T42" s="28">
         <f t="shared" si="1"/>
         <v>3884.3358346756763</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A43" s="16">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A43" s="13">
         <v>31</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="17">
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="14">
         <v>18.7</v>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="15">
         <v>458944</v>
       </c>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18">
+      <c r="J43" s="15"/>
+      <c r="K43" s="15">
         <v>458943.90600000002</v>
       </c>
-      <c r="L43" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M43" s="18">
+      <c r="L43" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" s="15">
         <v>153531.95300000001</v>
       </c>
-      <c r="N43" s="18">
+      <c r="N43" s="15">
         <v>4813.8029999999999</v>
       </c>
-      <c r="O43" s="16">
+      <c r="O43" s="13">
         <v>2.9889999999999999</v>
       </c>
-      <c r="P43" s="16"/>
-      <c r="Q43" s="19">
+      <c r="P43" s="13"/>
+      <c r="Q43" s="16">
         <v>20</v>
       </c>
-      <c r="R43" s="20">
+      <c r="R43" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S43" s="21">
+      <c r="S43" s="18">
         <f t="shared" si="0"/>
         <v>31.416000000000004</v>
       </c>
-      <c r="T43" s="33">
+      <c r="T43" s="27">
         <f t="shared" si="1"/>
         <v>6244.4841979725716</v>
       </c>
-      <c r="U43" s="21">
+      <c r="U43" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V43" s="24">
+      <c r="V43" s="21">
         <f>(S43-S31)*100/U43</f>
         <v>110.37681159420291</v>
       </c>
@@ -5613,69 +5575,69 @@
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A44" s="16">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A44" s="13">
         <v>32</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16">
-        <v>10.49</v>
-      </c>
-      <c r="G44" s="16"/>
-      <c r="H44" s="17">
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13">
+        <v>10.49</v>
+      </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="14">
         <v>18.34</v>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="15">
         <v>450574</v>
       </c>
-      <c r="J44" s="18"/>
-      <c r="K44" s="18">
+      <c r="J44" s="15"/>
+      <c r="K44" s="15">
         <v>450573.78100000002</v>
       </c>
-      <c r="L44" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M44" s="18">
+      <c r="L44" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="15">
         <v>148063.04699999999</v>
       </c>
-      <c r="N44" s="18">
+      <c r="N44" s="15">
         <v>3452.9059999999999</v>
       </c>
-      <c r="O44" s="16">
+      <c r="O44" s="13">
         <v>3.0430000000000001</v>
       </c>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="19">
+      <c r="P44" s="13"/>
+      <c r="Q44" s="16">
         <v>20</v>
       </c>
-      <c r="R44" s="20">
+      <c r="R44" s="17">
         <v>5.0309999999999997</v>
       </c>
-      <c r="S44" s="21">
+      <c r="S44" s="18">
         <f t="shared" si="0"/>
         <v>30.811200000000003</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="27">
         <f t="shared" si="1"/>
         <v>6124.2695289206931</v>
       </c>
-      <c r="U44" s="21">
+      <c r="U44" s="18">
         <f>0.05*569.25</f>
         <v>28.462500000000002</v>
       </c>
-      <c r="V44" s="24">
+      <c r="V44" s="21">
         <f>(S43-S32)*100/U44</f>
         <v>110.37681159420291</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>33</v>
       </c>
@@ -5712,16 +5674,16 @@
       <c r="R45" s="1">
         <v>5.0460000000000003</v>
       </c>
-      <c r="S45" s="14">
+      <c r="S45" s="11">
         <f t="shared" si="0"/>
         <v>27.3504</v>
       </c>
-      <c r="T45" s="34">
+      <c r="T45" s="28">
         <f t="shared" si="1"/>
         <v>5420.2140309155766</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>34</v>
       </c>
@@ -5758,16 +5720,16 @@
       <c r="R46" s="1">
         <v>5.0867000000000004</v>
       </c>
-      <c r="S46" s="14">
+      <c r="S46" s="11">
         <f t="shared" si="0"/>
         <v>27.686400000000003</v>
       </c>
-      <c r="T46" s="34">
+      <c r="T46" s="28">
         <f t="shared" si="1"/>
         <v>5442.9001120569328</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>35</v>
       </c>
@@ -5804,16 +5766,16 @@
       <c r="R47" s="1">
         <v>4.9630000000000001</v>
       </c>
-      <c r="S47" s="14">
+      <c r="S47" s="11">
         <f t="shared" si="0"/>
         <v>35.111999999999995</v>
       </c>
-      <c r="T47" s="34">
+      <c r="T47" s="28">
         <f t="shared" si="1"/>
         <v>7074.7531734837785</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>36</v>
       </c>
@@ -5850,16 +5812,16 @@
       <c r="R48" s="1">
         <v>5.0391000000000004</v>
       </c>
-      <c r="S48" s="14">
+      <c r="S48" s="11">
         <f t="shared" si="0"/>
         <v>36.758399999999995</v>
       </c>
-      <c r="T48" s="34">
+      <c r="T48" s="28">
         <f t="shared" si="1"/>
         <v>7294.6359468952769</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>37</v>
       </c>
@@ -5890,22 +5852,22 @@
       <c r="O49">
         <v>2.9489999999999998</v>
       </c>
-      <c r="Q49" s="28">
+      <c r="Q49" s="7">
         <v>60</v>
       </c>
-      <c r="R49" s="29">
+      <c r="R49" s="1">
         <v>5.0975999999999999</v>
       </c>
-      <c r="S49" s="30">
+      <c r="S49" s="11">
         <f t="shared" si="0"/>
         <v>182.75039999999998</v>
       </c>
-      <c r="T49" s="35">
+      <c r="T49" s="28">
         <f t="shared" si="1"/>
         <v>35850.282485875709</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>38</v>
       </c>
@@ -5936,22 +5898,22 @@
       <c r="O50">
         <v>3.048</v>
       </c>
-      <c r="Q50" s="28">
+      <c r="Q50" s="7">
         <v>60</v>
       </c>
-      <c r="R50" s="29">
+      <c r="R50" s="1">
         <v>4.9290000000000003</v>
       </c>
-      <c r="S50" s="30">
+      <c r="S50" s="11">
         <f t="shared" si="0"/>
         <v>178.11360000000002</v>
       </c>
-      <c r="T50" s="35">
+      <c r="T50" s="28">
         <f t="shared" si="1"/>
         <v>36135.849056603773</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>39</v>
       </c>
@@ -5982,22 +5944,22 @@
       <c r="O51">
         <v>3.0230000000000001</v>
       </c>
-      <c r="Q51" s="28">
+      <c r="Q51" s="7">
         <v>60</v>
       </c>
-      <c r="R51" s="29">
+      <c r="R51" s="1">
         <v>4.992</v>
       </c>
-      <c r="S51" s="30">
+      <c r="S51" s="11">
         <f t="shared" si="0"/>
         <v>321.55199999999996</v>
       </c>
-      <c r="T51" s="35">
+      <c r="T51" s="28">
         <f t="shared" si="1"/>
         <v>64413.461538461524</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>40</v>
       </c>
@@ -6028,22 +5990,22 @@
       <c r="O52">
         <v>3.1120000000000001</v>
       </c>
-      <c r="Q52" s="28">
+      <c r="Q52" s="7">
         <v>60</v>
       </c>
-      <c r="R52" s="29">
+      <c r="R52" s="1">
         <v>5.0566000000000004</v>
       </c>
-      <c r="S52" s="30">
+      <c r="S52" s="11">
         <f t="shared" si="0"/>
         <v>342.06480000000005</v>
       </c>
-      <c r="T52" s="35">
+      <c r="T52" s="28">
         <f t="shared" si="1"/>
         <v>67647.193766562516</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>41</v>
       </c>
@@ -6074,22 +6036,22 @@
       <c r="O53">
         <v>3.0579999999999998</v>
       </c>
-      <c r="Q53" s="28">
+      <c r="Q53" s="7">
         <v>60</v>
       </c>
-      <c r="R53" s="29">
+      <c r="R53" s="1">
         <v>4.9340000000000002</v>
       </c>
-      <c r="S53" s="30">
+      <c r="S53" s="11">
         <f t="shared" si="0"/>
         <v>456.27120000000002</v>
       </c>
-      <c r="T53" s="35">
+      <c r="T53" s="28">
         <f t="shared" si="1"/>
         <v>92474.908796108633</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>42</v>
       </c>
@@ -6120,22 +6082,22 @@
       <c r="O54">
         <v>2.98</v>
       </c>
-      <c r="Q54" s="28">
+      <c r="Q54" s="7">
         <v>60</v>
       </c>
-      <c r="R54" s="29">
+      <c r="R54" s="1">
         <v>5.0629999999999997</v>
       </c>
-      <c r="S54" s="30">
+      <c r="S54" s="11">
         <f t="shared" si="0"/>
         <v>568.05839999999989</v>
       </c>
-      <c r="T54" s="35">
+      <c r="T54" s="28">
         <f t="shared" si="1"/>
         <v>112197.98538415958</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>43</v>
       </c>
@@ -6166,22 +6128,22 @@
       <c r="O55">
         <v>2.9449999999999998</v>
       </c>
-      <c r="Q55" s="28">
+      <c r="Q55" s="7">
         <v>60</v>
       </c>
-      <c r="R55" s="29">
+      <c r="R55" s="1">
         <v>4.9804000000000004</v>
       </c>
-      <c r="S55" s="30">
+      <c r="S55" s="11">
         <f t="shared" si="0"/>
         <v>636.14879999999994</v>
       </c>
-      <c r="T55" s="35">
+      <c r="T55" s="28">
         <f t="shared" si="1"/>
         <v>127730.46341659302</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>44</v>
       </c>
@@ -6212,22 +6174,22 @@
       <c r="O56">
         <v>3.004</v>
       </c>
-      <c r="Q56" s="28">
+      <c r="Q56" s="7">
         <v>60</v>
       </c>
-      <c r="R56" s="29">
+      <c r="R56" s="1">
         <v>5.0620000000000003</v>
       </c>
-      <c r="S56" s="30">
+      <c r="S56" s="11">
         <f t="shared" si="0"/>
         <v>635.44319999999993</v>
       </c>
-      <c r="T56" s="35">
+      <c r="T56" s="28">
         <f t="shared" si="1"/>
         <v>125532.04267088106</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>45</v>
       </c>
@@ -6257,7 +6219,7 @@
       </c>
       <c r="Q57" s="7"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>46</v>
       </c>
@@ -6287,7 +6249,7 @@
       </c>
       <c r="Q58" s="7"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>47</v>
       </c>
@@ -6316,7 +6278,7 @@
         <v>3.0619999999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>48</v>
       </c>
@@ -6345,7 +6307,7 @@
         <v>4.0970000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>53</v>
       </c>
@@ -6374,7 +6336,7 @@
         <v>3.0169999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>54</v>
       </c>
@@ -6403,7 +6365,7 @@
         <v>3.0750000000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>55</v>
       </c>
@@ -6440,34 +6402,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.90625" customWidth="1"/>
-    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1796875" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" customWidth="1"/>
-    <col min="6" max="6" width="4.7265625" customWidth="1"/>
-    <col min="7" max="7" width="6.81640625" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" style="2"/>
-    <col min="9" max="13" width="10.90625" style="3"/>
-    <col min="14" max="14" width="6.6328125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="8.81640625" customWidth="1"/>
-    <col min="16" max="16" width="2.7265625" customWidth="1"/>
-    <col min="17" max="17" width="17.54296875" customWidth="1"/>
-    <col min="18" max="18" width="19.6328125" customWidth="1"/>
-    <col min="19" max="19" width="10.90625" style="14"/>
-    <col min="20" max="20" width="11.90625" style="14" customWidth="1"/>
-    <col min="21" max="21" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" customWidth="1"/>
+    <col min="4" max="4" width="8.5" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="2"/>
+    <col min="9" max="13" width="10.83203125" style="3"/>
+    <col min="14" max="14" width="6.6640625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="8.83203125" customWidth="1"/>
+    <col min="16" max="16" width="2.6640625" customWidth="1"/>
+    <col min="17" max="17" width="17.5" customWidth="1"/>
+    <col min="18" max="18" width="19.6640625" customWidth="1"/>
+    <col min="19" max="19" width="10.83203125" style="11"/>
+    <col min="20" max="20" width="11.83203125" style="11" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -6511,7 +6473,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6552,7 +6514,7 @@
         <v>1.077</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -6593,7 +6555,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -6634,7 +6596,7 @@
         <v>1.056</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -6675,7 +6637,7 @@
         <v>1.034</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>8</v>
       </c>
@@ -6716,7 +6678,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>38</v>
       </c>
@@ -6757,7 +6719,7 @@
         <v>1.157</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>39</v>
       </c>
@@ -6798,7 +6760,7 @@
         <v>1.056</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>40</v>
       </c>
@@ -6839,7 +6801,7 @@
         <v>1.091</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>41</v>
       </c>
@@ -6880,7 +6842,7 @@
         <v>1.1739999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>42</v>
       </c>
@@ -6921,7 +6883,7 @@
         <v>1.0920000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>43</v>
       </c>
@@ -6962,7 +6924,7 @@
         <v>1.056</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>44</v>
       </c>
@@ -7003,7 +6965,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>45</v>
       </c>
@@ -7044,7 +7006,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>46</v>
       </c>
@@ -7085,7 +7047,7 @@
         <v>1.083</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>47</v>
       </c>
@@ -7126,7 +7088,7 @@
         <v>1.054</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>5</v>
       </c>
@@ -7155,7 +7117,7 @@
         <v>1.0129999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>6</v>
       </c>
@@ -7184,7 +7146,7 @@
         <v>1.345</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>7</v>
       </c>
@@ -7192,7 +7154,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" ht="32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>9</v>
       </c>
@@ -7202,13 +7164,13 @@
       <c r="Q22" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="R22" s="13" t="s">
+      <c r="R22" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="S22" s="14" t="s">
+      <c r="S22" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="T22" s="46" t="s">
+      <c r="T22" s="39" t="s">
         <v>130</v>
       </c>
       <c r="U22" t="s">
@@ -7221,7 +7183,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>10</v>
       </c>
@@ -7252,23 +7214,23 @@
       <c r="O23">
         <v>1.103</v>
       </c>
-      <c r="Q23" s="37">
+      <c r="Q23" s="30">
         <v>4.9630000000000001</v>
       </c>
-      <c r="R23" s="25">
+      <c r="R23" s="22">
         <f>(H23*1.2/1000)*(7/0.4)</f>
         <v>2.5199999999999997E-3</v>
       </c>
-      <c r="S23" s="14">
+      <c r="S23" s="11">
         <f>R23*1000/Q23</f>
         <v>0.50775740479548648</v>
       </c>
-      <c r="T23" s="14">
+      <c r="T23" s="11">
         <f>S23*100/$W$35</f>
         <v>0.72041211419074402</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>11</v>
       </c>
@@ -7296,15 +7258,15 @@
       <c r="O24">
         <v>1.282</v>
       </c>
-      <c r="Q24" s="37">
+      <c r="Q24" s="30">
         <v>5.0391000000000004</v>
       </c>
-      <c r="R24" s="25">
+      <c r="R24" s="22">
         <f t="shared" ref="R24:R44" si="0">(H24*1.2/1000)*(7/0.4)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>12</v>
       </c>
@@ -7332,15 +7294,15 @@
       <c r="O25">
         <v>0.93200000000000005</v>
       </c>
-      <c r="Q25" s="37">
+      <c r="Q25" s="30">
         <v>4.9804000000000004</v>
       </c>
-      <c r="R25" s="25">
+      <c r="R25" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>13</v>
       </c>
@@ -7368,15 +7330,15 @@
       <c r="O26">
         <v>1.079</v>
       </c>
-      <c r="Q26" s="37">
+      <c r="Q26" s="30">
         <v>5.0620000000000003</v>
       </c>
-      <c r="R26" s="25">
+      <c r="R26" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>14</v>
       </c>
@@ -7407,23 +7369,23 @@
       <c r="O27">
         <v>1.0469999999999999</v>
       </c>
-      <c r="Q27" s="37">
+      <c r="Q27" s="30">
         <v>5.0460000000000003</v>
       </c>
-      <c r="R27" s="25">
+      <c r="R27" s="22">
         <f t="shared" si="0"/>
         <v>1.848E-2</v>
       </c>
-      <c r="S27" s="14">
+      <c r="S27" s="11">
         <f t="shared" ref="S27:S44" si="1">R27*1000/Q27</f>
         <v>3.6623067776456599</v>
       </c>
-      <c r="T27" s="14">
+      <c r="T27" s="11">
         <f t="shared" ref="T27:T34" si="2">S27*100/$W$35</f>
         <v>5.196123470737918</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>15</v>
       </c>
@@ -7454,23 +7416,23 @@
       <c r="O28">
         <v>1.1160000000000001</v>
       </c>
-      <c r="Q28" s="37">
+      <c r="Q28" s="30">
         <v>5.0867000000000004</v>
       </c>
-      <c r="R28" s="25">
+      <c r="R28" s="22">
         <f t="shared" si="0"/>
         <v>1.9529999999999999E-2</v>
       </c>
-      <c r="S28" s="14">
+      <c r="S28" s="11">
         <f t="shared" si="1"/>
         <v>3.8394243812294802</v>
       </c>
-      <c r="T28" s="14">
+      <c r="T28" s="11">
         <f t="shared" si="2"/>
         <v>5.4474199876436868</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>16</v>
       </c>
@@ -7501,23 +7463,23 @@
       <c r="O29">
         <v>1.115</v>
       </c>
-      <c r="Q29" s="37">
+      <c r="Q29" s="30">
         <v>5.0216000000000003</v>
       </c>
-      <c r="R29" s="25">
+      <c r="R29" s="22">
         <f t="shared" si="0"/>
         <v>3.4020000000000002E-2</v>
       </c>
-      <c r="S29" s="14">
+      <c r="S29" s="11">
         <f t="shared" si="1"/>
         <v>6.7747331527799908</v>
       </c>
-      <c r="T29" s="14">
+      <c r="T29" s="11">
         <f t="shared" si="2"/>
         <v>9.6120702279825085</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>17</v>
       </c>
@@ -7548,23 +7510,23 @@
       <c r="O30">
         <v>1.034</v>
       </c>
-      <c r="Q30" s="37">
+      <c r="Q30" s="30">
         <v>5.0906000000000002</v>
       </c>
-      <c r="R30" s="25">
+      <c r="R30" s="22">
         <f t="shared" si="0"/>
         <v>3.3180000000000001E-2</v>
       </c>
-      <c r="S30" s="14">
+      <c r="S30" s="11">
         <f t="shared" si="1"/>
         <v>6.5178957293835698</v>
       </c>
-      <c r="T30" s="14">
+      <c r="T30" s="11">
         <f t="shared" si="2"/>
         <v>9.2476663031065236</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>18</v>
       </c>
@@ -7595,23 +7557,23 @@
       <c r="O31">
         <v>1.137</v>
       </c>
-      <c r="Q31" s="37">
+      <c r="Q31" s="30">
         <v>4.9870000000000001</v>
       </c>
-      <c r="R31" s="25">
+      <c r="R31" s="22">
         <f t="shared" si="0"/>
         <v>4.3889999999999992E-2</v>
       </c>
-      <c r="S31" s="14">
+      <c r="S31" s="11">
         <f t="shared" si="1"/>
         <v>8.800882293964305</v>
       </c>
-      <c r="T31" s="14">
+      <c r="T31" s="11">
         <f t="shared" si="2"/>
         <v>12.486794205773187</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>19</v>
       </c>
@@ -7642,23 +7604,23 @@
       <c r="O32">
         <v>1.0820000000000001</v>
       </c>
-      <c r="Q32" s="37">
+      <c r="Q32" s="30">
         <v>4.9539999999999997</v>
       </c>
-      <c r="R32" s="25">
+      <c r="R32" s="22">
         <f t="shared" si="0"/>
         <v>4.5360000000000004E-2</v>
       </c>
-      <c r="S32" s="14">
+      <c r="S32" s="11">
         <f t="shared" si="1"/>
         <v>9.1562373839321776</v>
       </c>
-      <c r="T32" s="14">
+      <c r="T32" s="11">
         <f t="shared" si="2"/>
         <v>12.990976142332652</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>20</v>
       </c>
@@ -7689,23 +7651,23 @@
       <c r="O33">
         <v>1.0960000000000001</v>
       </c>
-      <c r="Q33" s="37">
+      <c r="Q33" s="30">
         <v>4.95</v>
       </c>
-      <c r="R33" s="25">
+      <c r="R33" s="22">
         <f t="shared" si="0"/>
         <v>7.6859999999999998E-2</v>
       </c>
-      <c r="S33" s="14">
+      <c r="S33" s="11">
         <f t="shared" si="1"/>
         <v>15.527272727272727</v>
       </c>
-      <c r="T33" s="14">
+      <c r="T33" s="11">
         <f t="shared" si="2"/>
         <v>22.030275220853383</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>21</v>
       </c>
@@ -7736,148 +7698,148 @@
       <c r="O34">
         <v>1.0880000000000001</v>
       </c>
-      <c r="Q34" s="37">
+      <c r="Q34" s="30">
         <v>4.9661999999999997</v>
       </c>
-      <c r="R34" s="25">
+      <c r="R34" s="22">
         <f t="shared" si="0"/>
         <v>7.6020000000000004E-2</v>
       </c>
-      <c r="S34" s="14">
+      <c r="S34" s="11">
         <f t="shared" si="1"/>
         <v>15.30747855503202</v>
       </c>
-      <c r="T34" s="14">
+      <c r="T34" s="11">
         <f t="shared" si="2"/>
         <v>21.718428691752525</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A35" s="16">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A35" s="13">
         <v>22</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16">
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13">
         <v>6.23</v>
       </c>
-      <c r="G35" s="16"/>
-      <c r="H35" s="17">
+      <c r="G35" s="13"/>
+      <c r="H35" s="14">
         <v>16.18</v>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="15">
         <v>33314</v>
       </c>
-      <c r="J35" s="18"/>
-      <c r="K35" s="18">
+      <c r="J35" s="15"/>
+      <c r="K35" s="15">
         <v>33313.684000000001</v>
       </c>
-      <c r="L35" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="18">
+      <c r="L35" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M35" s="15">
         <v>31556.708999999999</v>
       </c>
-      <c r="N35" s="18">
+      <c r="N35" s="15">
         <v>2311.5740000000001</v>
       </c>
-      <c r="O35" s="16">
+      <c r="O35" s="13">
         <v>1.056</v>
       </c>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="38">
+      <c r="P35" s="13"/>
+      <c r="Q35" s="31">
         <v>5.0309999999999997</v>
       </c>
-      <c r="R35" s="39">
+      <c r="R35" s="32">
         <f t="shared" si="0"/>
         <v>0.33977999999999997</v>
       </c>
-      <c r="S35" s="21">
+      <c r="S35" s="18">
         <f t="shared" si="1"/>
         <v>67.537268932617764</v>
       </c>
-      <c r="T35" s="21"/>
-      <c r="U35" s="20">
+      <c r="T35" s="18"/>
+      <c r="U35" s="17">
         <f>0.05*9.74</f>
         <v>0.48700000000000004</v>
       </c>
-      <c r="V35" s="24">
+      <c r="V35" s="21">
         <f>R35*100/U35</f>
         <v>69.770020533880881</v>
       </c>
-      <c r="W35" s="24">
+      <c r="W35" s="21">
         <f>AVERAGE(V35:V36)</f>
         <v>70.481519507186846</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A36" s="16">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A36" s="13">
         <v>23</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16">
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13">
         <v>6.23</v>
       </c>
-      <c r="G36" s="16"/>
-      <c r="H36" s="17">
+      <c r="G36" s="13"/>
+      <c r="H36" s="14">
         <v>16.510000000000002</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="15">
         <v>33953</v>
       </c>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18">
+      <c r="J36" s="15"/>
+      <c r="K36" s="15">
         <v>33952.934000000001</v>
       </c>
-      <c r="L36" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="M36" s="18">
+      <c r="L36" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" s="15">
         <v>31665.307000000001</v>
       </c>
-      <c r="N36" s="18">
+      <c r="N36" s="15">
         <v>3594.6759999999999</v>
       </c>
-      <c r="O36" s="16">
+      <c r="O36" s="13">
         <v>1.0720000000000001</v>
       </c>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="38">
+      <c r="P36" s="13"/>
+      <c r="Q36" s="31">
         <v>5.0309999999999997</v>
       </c>
-      <c r="R36" s="39">
+      <c r="R36" s="32">
         <f t="shared" si="0"/>
         <v>0.34671000000000002</v>
       </c>
-      <c r="S36" s="21">
+      <c r="S36" s="18">
         <f t="shared" si="1"/>
         <v>68.914728682170548</v>
       </c>
-      <c r="T36" s="21"/>
-      <c r="U36" s="20">
+      <c r="T36" s="18"/>
+      <c r="U36" s="17">
         <f>0.05*9.74</f>
         <v>0.48700000000000004</v>
       </c>
-      <c r="V36" s="24">
+      <c r="V36" s="21">
         <f>R36*100/U36</f>
         <v>71.19301848049281</v>
       </c>
-      <c r="W36" s="24"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W36" s="21"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>24</v>
       </c>
@@ -7908,23 +7870,23 @@
       <c r="O37">
         <v>1.054</v>
       </c>
-      <c r="Q37" s="37">
+      <c r="Q37" s="30">
         <v>4.9340000000000002</v>
       </c>
-      <c r="R37" s="25">
+      <c r="R37" s="22">
         <f t="shared" si="0"/>
         <v>0.34524000000000005</v>
       </c>
-      <c r="S37" s="14">
+      <c r="S37" s="11">
         <f t="shared" si="1"/>
         <v>69.971625456019467</v>
       </c>
-      <c r="T37" s="14">
+      <c r="T37" s="11">
         <f t="shared" ref="T37:T44" si="3">S37*100/$W$35</f>
         <v>99.276556387074791</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>25</v>
       </c>
@@ -7955,23 +7917,23 @@
       <c r="O38">
         <v>1.0840000000000001</v>
       </c>
-      <c r="Q38" s="37">
+      <c r="Q38" s="30">
         <v>5.0629999999999997</v>
       </c>
-      <c r="R38" s="25">
+      <c r="R38" s="22">
         <f t="shared" si="0"/>
         <v>0.35658000000000001</v>
       </c>
-      <c r="S38" s="14">
+      <c r="S38" s="11">
         <f t="shared" si="1"/>
         <v>70.428599644479561</v>
       </c>
-      <c r="T38" s="14">
+      <c r="T38" s="11">
         <f t="shared" si="3"/>
         <v>99.924916683015198</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>26</v>
       </c>
@@ -8002,23 +7964,23 @@
       <c r="O39">
         <v>1.032</v>
       </c>
-      <c r="Q39" s="37">
+      <c r="Q39" s="30">
         <v>4.992</v>
       </c>
-      <c r="R39" s="25">
+      <c r="R39" s="22">
         <f t="shared" si="0"/>
         <v>0.58253999999999995</v>
       </c>
-      <c r="S39" s="14">
+      <c r="S39" s="11">
         <f t="shared" si="1"/>
         <v>116.69471153846153</v>
       </c>
-      <c r="T39" s="14">
+      <c r="T39" s="11">
         <f t="shared" si="3"/>
         <v>165.56781459083388</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>27</v>
       </c>
@@ -8049,23 +8011,23 @@
       <c r="O40">
         <v>1.032</v>
       </c>
-      <c r="Q40" s="37">
+      <c r="Q40" s="30">
         <v>5.0566000000000004</v>
       </c>
-      <c r="R40" s="25">
+      <c r="R40" s="22">
         <f t="shared" si="0"/>
         <v>0.52163999999999999</v>
       </c>
-      <c r="S40" s="14">
+      <c r="S40" s="11">
         <f t="shared" si="1"/>
         <v>103.1602262389748</v>
       </c>
-      <c r="T40" s="14">
+      <c r="T40" s="11">
         <f t="shared" si="3"/>
         <v>146.36492936060461</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>28</v>
       </c>
@@ -8096,23 +8058,23 @@
       <c r="O41">
         <v>1.0720000000000001</v>
       </c>
-      <c r="Q41" s="37">
+      <c r="Q41" s="30">
         <v>5.0796000000000001</v>
       </c>
-      <c r="R41" s="25">
+      <c r="R41" s="22">
         <f t="shared" si="0"/>
         <v>1.2028800000000002</v>
       </c>
-      <c r="S41" s="14">
+      <c r="S41" s="11">
         <f t="shared" si="1"/>
         <v>236.80604772029295</v>
       </c>
-      <c r="T41" s="14">
+      <c r="T41" s="11">
         <f t="shared" si="3"/>
         <v>335.98317598153704</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>29</v>
       </c>
@@ -8143,23 +8105,23 @@
       <c r="O42">
         <v>1.0609999999999999</v>
       </c>
-      <c r="Q42" s="37">
+      <c r="Q42" s="30">
         <v>4.9290000000000003</v>
       </c>
-      <c r="R42" s="25">
+      <c r="R42" s="22">
         <f t="shared" si="0"/>
         <v>1.1831400000000001</v>
       </c>
-      <c r="S42" s="14">
+      <c r="S42" s="11">
         <f t="shared" si="1"/>
         <v>240.03651856360318</v>
       </c>
-      <c r="T42" s="14">
+      <c r="T42" s="11">
         <f t="shared" si="3"/>
         <v>340.56660560379544</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>30</v>
       </c>
@@ -8190,23 +8152,23 @@
       <c r="O43">
         <v>1.07</v>
       </c>
-      <c r="Q43" s="37">
+      <c r="Q43" s="30">
         <v>4.9333999999999998</v>
       </c>
-      <c r="R43" s="25">
+      <c r="R43" s="22">
         <f t="shared" si="0"/>
         <v>1.47021</v>
       </c>
-      <c r="S43" s="14">
+      <c r="S43" s="11">
         <f t="shared" si="1"/>
         <v>298.01151335792764</v>
       </c>
-      <c r="T43" s="14">
+      <c r="T43" s="11">
         <f t="shared" si="3"/>
         <v>422.82220281522177</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>31</v>
       </c>
@@ -8237,23 +8199,23 @@
       <c r="O44">
         <v>1.0780000000000001</v>
       </c>
-      <c r="Q44" s="37">
+      <c r="Q44" s="30">
         <v>4.9353999999999996</v>
       </c>
-      <c r="R44" s="25">
+      <c r="R44" s="22">
         <f t="shared" si="0"/>
         <v>1.4683199999999998</v>
       </c>
-      <c r="S44" s="14">
+      <c r="S44" s="11">
         <f t="shared" si="1"/>
         <v>297.50780078615719</v>
       </c>
-      <c r="T44" s="14">
+      <c r="T44" s="11">
         <f t="shared" si="3"/>
         <v>422.10752955719261</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>32</v>
       </c>
@@ -8281,10 +8243,10 @@
       <c r="O45">
         <v>1.1240000000000001</v>
       </c>
-      <c r="Q45" s="37"/>
-      <c r="R45" s="25"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Q45" s="30"/>
+      <c r="R45" s="22"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>33</v>
       </c>
@@ -8313,7 +8275,7 @@
         <v>1.605</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>34</v>
       </c>
@@ -8342,7 +8304,7 @@
         <v>0.90100000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>35</v>
       </c>
@@ -8350,7 +8312,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>36</v>
       </c>
@@ -8358,7 +8320,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>37</v>
       </c>
@@ -8366,7 +8328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -8378,7 +8340,7 @@
       <c r="M52"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="H53"/>
       <c r="I53"/>
       <c r="J53"/>
@@ -8387,7 +8349,7 @@
       <c r="M53"/>
       <c r="N53"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>1</v>
       </c>
@@ -8433,14 +8395,14 @@
       <c r="Q54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="R54" s="13" t="s">
+      <c r="R54" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="S54" s="14" t="s">
+      <c r="S54" s="11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1</v>
       </c>
@@ -8481,7 +8443,7 @@
         <v>1.165</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>2</v>
       </c>
@@ -8522,7 +8484,7 @@
         <v>1.131</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>3</v>
       </c>
@@ -8563,7 +8525,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4</v>
       </c>
@@ -8604,7 +8566,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>5</v>
       </c>
@@ -8645,7 +8607,7 @@
         <v>1.121</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>6</v>
       </c>
@@ -8686,7 +8648,7 @@
         <v>1.111</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>7</v>
       </c>
@@ -8727,7 +8689,7 @@
         <v>1.054</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>8</v>
       </c>
@@ -8768,7 +8730,7 @@
         <v>1.0349999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>9</v>
       </c>
@@ -8809,7 +8771,7 @@
         <v>1.077</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>10</v>
       </c>
@@ -8850,7 +8812,7 @@
         <v>1.081</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>11</v>
       </c>
@@ -8891,7 +8853,7 @@
         <v>1.056</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>12</v>
       </c>
@@ -8932,7 +8894,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>13</v>
       </c>
@@ -8964,7 +8926,7 @@
         <v>1.111</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>14</v>
       </c>
@@ -8996,7 +8958,7 @@
         <v>1.2250000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>15</v>
       </c>
@@ -9028,7 +8990,7 @@
         <v>1.552</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>16</v>
       </c>
@@ -9036,7 +8998,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>17</v>
       </c>
@@ -9044,7 +9006,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>18</v>
       </c>
@@ -9052,7 +9014,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>19</v>
       </c>
@@ -9081,7 +9043,7 @@
         <v>1.214</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>20</v>
       </c>
@@ -9110,104 +9072,104 @@
         <v>1.1040000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A75" s="40">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A75" s="33">
         <v>21</v>
       </c>
-      <c r="B75" s="40" t="s">
+      <c r="B75" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="40"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="40"/>
-      <c r="F75" s="40">
+      <c r="C75" s="33"/>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33"/>
+      <c r="F75" s="33">
         <v>6.23</v>
       </c>
-      <c r="G75" s="40"/>
-      <c r="H75" s="41"/>
-      <c r="I75" s="42">
+      <c r="G75" s="33"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="35">
         <v>106</v>
       </c>
-      <c r="J75" s="42"/>
-      <c r="K75" s="42">
+      <c r="J75" s="35"/>
+      <c r="K75" s="35">
         <v>106.16</v>
       </c>
-      <c r="L75" s="42" t="s">
+      <c r="L75" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="M75" s="42">
+      <c r="M75" s="35">
         <v>97.942999999999998</v>
       </c>
-      <c r="N75" s="42">
+      <c r="N75" s="35">
         <v>9.8040000000000003</v>
       </c>
-      <c r="O75" s="40">
+      <c r="O75" s="33">
         <v>1.0840000000000001</v>
       </c>
-      <c r="P75" s="40"/>
-      <c r="Q75" s="43">
+      <c r="P75" s="33"/>
+      <c r="Q75" s="36">
         <v>5.0263</v>
       </c>
-      <c r="R75" s="44">
+      <c r="R75" s="37">
         <f t="shared" ref="R75:R76" si="4">(H75*1.2/1000)*(7/0.4)</f>
         <v>0</v>
       </c>
-      <c r="S75" s="45">
+      <c r="S75" s="38">
         <f t="shared" ref="S75:S76" si="5">R75*1000/Q75</f>
         <v>0</v>
       </c>
-      <c r="T75" s="45">
+      <c r="T75" s="38">
         <f t="shared" ref="T75:T76" si="6">S75*100/$W$35</f>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A76" s="40">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A76" s="33">
         <v>22</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B76" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="40"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="40"/>
-      <c r="F76" s="40">
+      <c r="C76" s="33"/>
+      <c r="D76" s="33"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="33">
         <v>6.25</v>
       </c>
-      <c r="G76" s="40"/>
-      <c r="H76" s="41"/>
-      <c r="I76" s="42">
+      <c r="G76" s="33"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="35">
         <v>138</v>
       </c>
-      <c r="J76" s="42"/>
-      <c r="K76" s="42">
+      <c r="J76" s="35"/>
+      <c r="K76" s="35">
         <v>138.16200000000001</v>
       </c>
-      <c r="L76" s="42" t="s">
+      <c r="L76" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="M76" s="42">
+      <c r="M76" s="35">
         <v>104.468</v>
       </c>
-      <c r="N76" s="42">
+      <c r="N76" s="35">
         <v>14.14</v>
       </c>
-      <c r="O76" s="40">
+      <c r="O76" s="33">
         <v>1.3220000000000001</v>
       </c>
-      <c r="P76" s="40"/>
-      <c r="Q76" s="43">
+      <c r="P76" s="33"/>
+      <c r="Q76" s="36">
         <v>4.96</v>
       </c>
-      <c r="R76" s="44">
+      <c r="R76" s="37">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S76" s="45">
+      <c r="S76" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T76" s="45">
+      <c r="T76" s="38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -9222,493 +9184,564 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="1.453125" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="1.5" customWidth="1"/>
+    <col min="12" max="13" width="10.83203125" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="D1" s="62" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="D1" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="62" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-    </row>
-    <row r="2" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+    </row>
+    <row r="2" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="50" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="52" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" s="58" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="51" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52">
+      <c r="C3" s="44"/>
+      <c r="D3" s="45">
         <v>0</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="45">
         <v>0</v>
       </c>
-      <c r="F3" s="60">
+      <c r="F3" s="53">
         <f>AVERAGE(D3:E3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="49"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="54">
+      <c r="G3" s="42"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="47">
         <f>'dose_epx_gamme basse'!T31</f>
         <v>0.20890117979428208</v>
       </c>
-      <c r="J3" s="54">
+      <c r="J3" s="47">
         <f>'dose_epx_gamme basse'!T32</f>
         <v>0.16935483870967744</v>
       </c>
-      <c r="K3" s="61">
+      <c r="K3" s="54">
         <f>AVERAGE(I3:J3)</f>
         <v>0.18912800925197976</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="58">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="51">
         <v>2</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="48">
         <v>0</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="45">
         <f>dose_imd!T23</f>
         <v>0.72041211419074402</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="45">
         <v>0</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="53">
         <f t="shared" ref="F4:F13" si="0">AVERAGE(D4:E4)</f>
         <v>0.36020605709537201</v>
       </c>
-      <c r="G4" s="49"/>
-      <c r="H4" s="56">
+      <c r="G4" s="42"/>
+      <c r="H4" s="49">
         <v>9418.1</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="47">
         <f>'dose_epx_gamme basse'!T47</f>
         <v>6797.1791255289127</v>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="47">
         <f>'dose_epx_gamme basse'!T48</f>
         <v>7021.253795320592</v>
       </c>
-      <c r="K4" s="61">
+      <c r="K4" s="54">
         <f t="shared" ref="K4:K13" si="1">AVERAGE(I4:J4)</f>
         <v>6909.2164604247519</v>
       </c>
-      <c r="L4" s="34"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" s="58">
+      <c r="L4" s="56">
+        <f>K4/H4</f>
+        <v>0.73361043739445875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="51">
         <v>2</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="48">
         <v>6.5</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="45">
         <f>dose_imd!T27</f>
         <v>5.196123470737918</v>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="45">
         <f>dose_imd!T28</f>
         <v>5.4474199876436868</v>
       </c>
-      <c r="F5" s="60">
+      <c r="F5" s="53">
         <f t="shared" si="0"/>
         <v>5.321771729190802</v>
       </c>
-      <c r="G5" s="49"/>
-      <c r="H5" s="56">
+      <c r="G5" s="42"/>
+      <c r="H5" s="49">
         <v>7063.6</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="47">
         <f>'dose_epx_gamme basse'!T45</f>
         <v>5157.1938168846609</v>
       </c>
-      <c r="J5" s="54">
+      <c r="J5" s="47">
         <f>'dose_epx_gamme basse'!T46</f>
         <v>5181.9843906658534</v>
       </c>
-      <c r="K5" s="61">
+      <c r="K5" s="54">
         <f t="shared" si="1"/>
         <v>5169.5891037752572</v>
       </c>
-      <c r="L5" s="34"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="58">
+      <c r="L5" s="56">
+        <f t="shared" ref="L5:L13" si="2">K5/H5</f>
+        <v>0.7318632289165945</v>
+      </c>
+      <c r="M5" s="56">
+        <f t="shared" ref="M5:M13" si="3">F5/C5</f>
+        <v>0.81873411218320036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="51">
         <v>2</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="48">
         <v>13.1</v>
       </c>
-      <c r="D6" s="52">
+      <c r="D6" s="45">
         <f>dose_imd!T29</f>
         <v>9.6120702279825085</v>
       </c>
-      <c r="E6" s="52">
+      <c r="E6" s="45">
         <f>dose_imd!T30</f>
         <v>9.2476663031065236</v>
       </c>
-      <c r="F6" s="60">
+      <c r="F6" s="53">
         <f t="shared" si="0"/>
         <v>9.429868265544517</v>
       </c>
-      <c r="G6" s="49"/>
-      <c r="H6" s="56">
+      <c r="G6" s="42"/>
+      <c r="H6" s="49">
         <v>4709</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="47">
         <f>'dose_epx_gamme basse'!T41</f>
         <v>3519.5156922096544</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="47">
         <f>'dose_epx_gamme basse'!T42</f>
         <v>3679.7234117785715</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="54">
         <f t="shared" si="1"/>
         <v>3599.619551994113</v>
       </c>
-      <c r="L6" s="34"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" s="58">
+      <c r="L6" s="56">
+        <f t="shared" si="2"/>
+        <v>0.76441273136422017</v>
+      </c>
+      <c r="M6" s="56">
+        <f t="shared" si="3"/>
+        <v>0.71983727217897076</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="51">
         <v>2</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="48">
         <v>19.600000000000001</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="45">
         <f>dose_imd!T31</f>
         <v>12.486794205773187</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="45">
         <f>dose_imd!T32</f>
         <v>12.990976142332652</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="53">
         <f t="shared" si="0"/>
         <v>12.738885174052919</v>
       </c>
-      <c r="G7" s="49"/>
-      <c r="H7" s="56">
+      <c r="G7" s="42"/>
+      <c r="H7" s="49">
         <v>2354.5</v>
       </c>
-      <c r="I7" s="54">
+      <c r="I7" s="47">
         <f>'dose_epx_gamme basse'!T39</f>
         <v>1418.247443352717</v>
       </c>
-      <c r="J7" s="54">
+      <c r="J7" s="47">
         <f>'dose_epx_gamme basse'!T40</f>
         <v>2173.7585789261202</v>
       </c>
-      <c r="K7" s="61">
+      <c r="K7" s="54">
         <f t="shared" si="1"/>
         <v>1796.0030111394185</v>
       </c>
-      <c r="L7" s="34"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="58">
+      <c r="L7" s="56">
+        <f t="shared" si="2"/>
+        <v>0.76279592743232894</v>
+      </c>
+      <c r="M7" s="56">
+        <f t="shared" si="3"/>
+        <v>0.64994312112514885</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="51">
         <v>2</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="48">
         <v>26.1</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="45">
         <f>dose_imd!T33</f>
         <v>22.030275220853383</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="45">
         <f>dose_imd!T34</f>
         <v>21.718428691752525</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="53">
         <f t="shared" si="0"/>
         <v>21.874351956302952</v>
       </c>
-      <c r="G8" s="49"/>
-      <c r="H8" s="56">
+      <c r="G8" s="42"/>
+      <c r="H8" s="49">
         <v>0</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="47">
         <f>'dose_epx_gamme basse'!T33</f>
         <v>0</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="47">
         <f>'dose_epx_gamme basse'!T34</f>
         <v>3.3830044301248492</v>
       </c>
-      <c r="K8" s="61">
+      <c r="K8" s="54">
         <f t="shared" si="1"/>
         <v>1.6915022150624246</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9" s="58">
+      <c r="M8" s="56">
+        <f t="shared" si="3"/>
+        <v>0.8380977761035614</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="51">
         <v>5</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="48">
         <f>C4*18</f>
         <v>0</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="45">
         <v>0</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="45">
         <v>0</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="53">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G9" s="49"/>
-      <c r="H9" s="56">
+      <c r="G9" s="42"/>
+      <c r="H9" s="49">
         <f>H4*18</f>
         <v>169525.80000000002</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="47">
         <f>'dose_epx_gamme haute'!T55</f>
         <v>127730.46341659302</v>
       </c>
-      <c r="J9" s="54">
+      <c r="J9" s="47">
         <f>'dose_epx_gamme haute'!T56</f>
         <v>125532.04267088106</v>
       </c>
-      <c r="K9" s="61">
+      <c r="K9" s="54">
         <f t="shared" si="1"/>
         <v>126631.25304373703</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="58">
+      <c r="L9" s="56">
+        <f t="shared" si="2"/>
+        <v>0.74697334000923177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="51">
         <v>5</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="55">
-        <f t="shared" ref="C10:C13" si="2">C5*18</f>
+      <c r="C10" s="48">
+        <f t="shared" ref="C10:C13" si="4">C5*18</f>
         <v>117</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="45">
         <f>dose_imd!T37</f>
         <v>99.276556387074791</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="45">
         <f>dose_imd!T38</f>
         <v>99.924916683015198</v>
       </c>
-      <c r="F10" s="60">
+      <c r="F10" s="53">
         <f t="shared" si="0"/>
         <v>99.600736535045002</v>
       </c>
-      <c r="G10" s="49"/>
-      <c r="H10" s="56">
+      <c r="G10" s="42"/>
+      <c r="H10" s="49">
         <f>H5*18</f>
         <v>127144.8</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="47">
         <f>'dose_epx_gamme haute'!T53</f>
         <v>92474.908796108633</v>
       </c>
-      <c r="J10" s="54">
+      <c r="J10" s="47">
         <f>'dose_epx_gamme haute'!T54</f>
         <v>112197.98538415958</v>
       </c>
-      <c r="K10" s="61">
+      <c r="K10" s="54">
         <f t="shared" si="1"/>
         <v>102336.44709013411</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="58">
+      <c r="L10" s="56">
+        <f t="shared" si="2"/>
+        <v>0.80488110477293695</v>
+      </c>
+      <c r="M10" s="56">
+        <f t="shared" si="3"/>
+        <v>0.85128834645337603</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="51">
         <v>5</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="55">
-        <f t="shared" si="2"/>
+      <c r="C11" s="48">
+        <f t="shared" si="4"/>
         <v>235.79999999999998</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="45">
         <f>dose_imd!T39</f>
         <v>165.56781459083388</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="45">
         <f>dose_imd!T40</f>
         <v>146.36492936060461</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="53">
         <f t="shared" si="0"/>
         <v>155.96637197571926</v>
       </c>
-      <c r="G11" s="49"/>
-      <c r="H11" s="56">
+      <c r="G11" s="42"/>
+      <c r="H11" s="49">
         <f>H6*18</f>
         <v>84762</v>
       </c>
-      <c r="I11" s="54">
+      <c r="I11" s="47">
         <f>'dose_epx_gamme haute'!T51</f>
         <v>64413.461538461524</v>
       </c>
-      <c r="J11" s="54">
+      <c r="J11" s="47">
         <f>'dose_epx_gamme haute'!T52</f>
         <v>67647.193766562516</v>
       </c>
-      <c r="K11" s="61">
+      <c r="K11" s="54">
         <f t="shared" si="1"/>
         <v>66030.327652512016</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="58">
+      <c r="L11" s="56">
+        <f t="shared" si="2"/>
+        <v>0.77900860825030105</v>
+      </c>
+      <c r="M11" s="56">
+        <f t="shared" si="3"/>
+        <v>0.66143499565614616</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="51">
         <v>5</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="51" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="55">
-        <f t="shared" si="2"/>
+      <c r="C12" s="48">
+        <f t="shared" si="4"/>
         <v>352.8</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="45">
         <f>dose_imd!T41</f>
         <v>335.98317598153704</v>
       </c>
-      <c r="E12" s="52">
+      <c r="E12" s="45">
         <f>dose_imd!T42</f>
         <v>340.56660560379544</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="53">
         <f t="shared" si="0"/>
         <v>338.27489079266627</v>
       </c>
-      <c r="G12" s="49"/>
-      <c r="H12" s="56">
+      <c r="G12" s="42"/>
+      <c r="H12" s="49">
         <f>H7*18</f>
         <v>42381</v>
       </c>
-      <c r="I12" s="54">
+      <c r="I12" s="47">
         <f>'dose_epx_gamme haute'!T49</f>
         <v>35850.282485875709</v>
       </c>
-      <c r="J12" s="54">
+      <c r="J12" s="47">
         <f>'dose_epx_gamme haute'!T50</f>
         <v>36135.849056603773</v>
       </c>
-      <c r="K12" s="61">
+      <c r="K12" s="54">
         <f t="shared" si="1"/>
         <v>35993.065771239737</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="58">
+      <c r="L12" s="56">
+        <f t="shared" si="2"/>
+        <v>0.84927363137348666</v>
+      </c>
+      <c r="M12" s="56">
+        <f t="shared" si="3"/>
+        <v>0.95882905553476827</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="51">
         <v>5</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="C13" s="55">
-        <f t="shared" si="2"/>
+      <c r="C13" s="48">
+        <f t="shared" si="4"/>
         <v>469.8</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="45">
         <f>dose_imd!T43</f>
         <v>422.82220281522177</v>
       </c>
-      <c r="E13" s="52">
+      <c r="E13" s="45">
         <f>dose_imd!T44</f>
         <v>422.10752955719261</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="53">
         <f t="shared" si="0"/>
         <v>422.46486618620719</v>
       </c>
-      <c r="G13" s="49"/>
-      <c r="H13" s="56">
+      <c r="G13" s="42"/>
+      <c r="H13" s="49">
         <f>H8*18</f>
         <v>0</v>
       </c>
-      <c r="I13" s="54">
+      <c r="I13" s="47">
         <f>'dose_epx_gamme basse'!T35</f>
         <v>0</v>
       </c>
-      <c r="J13" s="54">
+      <c r="J13" s="47">
         <f>'dose_epx_gamme basse'!T36</f>
         <v>0</v>
       </c>
-      <c r="K13" s="61">
+      <c r="K13" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="M13" s="56">
+        <f t="shared" si="3"/>
+        <v>0.8992440744704282</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L15" s="56">
+        <f>AVERAGE(L4:L12)</f>
+        <v>0.77160237618919492</v>
+      </c>
+      <c r="M15" s="56">
+        <f>AVERAGE(M4:M13)</f>
+        <v>0.79967609421320007</v>
       </c>
     </row>
   </sheetData>
